--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451143.5075163038</v>
+        <v>451144</v>
       </c>
       <c r="R2" t="n">
-        <v>6440741.449745786</v>
+        <v>6440741</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1984-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>96819</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451143.5075163038</v>
+        <v>451144</v>
       </c>
       <c r="R3" t="n">
-        <v>6440741.449745786</v>
+        <v>6440741</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +844,9 @@
           <t>1984-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>96253</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451143.5075163038</v>
+        <v>451144</v>
       </c>
       <c r="R4" t="n">
-        <v>6440741.449745786</v>
+        <v>6440741</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -976,19 +941,9 @@
           <t>1984-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,12 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451143.5075163038</v>
+        <v>451144</v>
       </c>
       <c r="R5" t="n">
-        <v>6440741.449745786</v>
+        <v>6440741</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1092,19 +1042,9 @@
           <t>1984-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1984-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,12 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>106706</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451143.5075163038</v>
+        <v>451144</v>
       </c>
       <c r="R6" t="n">
-        <v>6440741.449745786</v>
+        <v>6440741</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1208,19 +1143,9 @@
           <t>1984-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-07-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99091</v>
+        <v>99105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98491</v>
+        <v>98505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109134</v>
+        <v>109158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99105</v>
+        <v>99108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109158</v>
+        <v>109171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99108</v>
+        <v>99113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99113</v>
+        <v>99114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99114</v>
+        <v>99141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99141</v>
+        <v>99154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98539</v>
+        <v>98552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109213</v>
+        <v>109226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99154</v>
+        <v>99158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>2763534</v>
       </c>
       <c r="B2" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5103138</v>
       </c>
       <c r="B3" t="n">
-        <v>99158</v>
+        <v>99165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>5945191</v>
       </c>
       <c r="B4" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>4185140</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>2660135</v>
       </c>
       <c r="B6" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2763534</v>
+        <v>2660135</v>
       </c>
       <c r="B2" t="n">
-        <v>109505</v>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5103138</v>
+        <v>2763534</v>
       </c>
       <c r="B3" t="n">
-        <v>99168</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222541</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5945191</v>
+        <v>4185140</v>
       </c>
       <c r="B4" t="n">
-        <v>98566</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,19 +888,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,27 +978,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4185140</v>
+        <v>5103138</v>
       </c>
       <c r="B5" t="n">
-        <v>97517</v>
+        <v>99646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222541</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,34 +1079,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2660135</v>
+        <v>5945191</v>
       </c>
       <c r="B6" t="n">
-        <v>109241</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 23272-2025 artfynd.xlsx
+++ b/artfynd/A 23272-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2660135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2763534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4185140</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5103138</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,8 +1198,20 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5945191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>